--- a/output/2026-summer_夏合宿収支報告.xlsx
+++ b/output/2026-summer_夏合宿収支報告.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,10 +96,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -472,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -496,7 +495,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46256</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="3">
@@ -618,75 +617,75 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>顧問宿泊費・交通費・昼食代（別財源）</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
-        <f>B14*C14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>収入合計</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="11">
-        <f>SUM(D10:D14)</f>
-        <v/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="9">
+        <f>SUM(D10:D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>【支出】</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>【支出】</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>費目</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>金額</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>費目</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>単価</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>金額</t>
-        </is>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ホテル宿泊代（1泊3食）</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>9130</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>258</v>
+      </c>
+      <c r="D18" s="7">
+        <f>B18*C18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ホテル宿泊代（1泊3食）</t>
+          <t>増（追加）昼食代</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>9130</v>
+        <v>1100</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>258</v>
+        <v>44</v>
       </c>
       <c r="D19" s="7">
         <f>B19*C19</f>
@@ -696,7 +695,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>増（追加）昼食代</t>
+          <t>BBQ代</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
@@ -713,14 +712,14 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>BBQ代</t>
+          <t>グラウンド使用料</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1100</v>
+        <v>5500</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D21" s="7">
         <f>B21*C21</f>
@@ -734,10 +733,10 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>5500</v>
+        <v>11000</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D22" s="7">
         <f>B22*C22</f>
@@ -747,28 +746,33 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>グラウンド使用料</t>
+          <t>ホテル請求書との差異（増朝食・増夕食・増宿泊等）※1</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>11000</v>
+        <v>-1320</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D23" s="7">
         <f>B23*C23</f>
         <v/>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>簡易再構成モデルでは内訳化していない単発追加分</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>ホテル請求書との差異（増朝食・増夕食・増宿泊等）※1</t>
+          <t>雑費（合宿中の経費）※2</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>-1320</v>
+        <v>25894</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>1</v>
@@ -777,20 +781,15 @@
         <f>B24*C24</f>
         <v/>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>簡易再構成モデルでは内訳化していない単発追加分</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>雑費（合宿中の経費）※2</t>
+          <t>バス代（国際興業・見積額）※3</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>25894</v>
+        <v>445200</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>1</v>
@@ -803,11 +802,11 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>バス代（国際興業・見積額）※3</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>445200</v>
+          <t>コーチ宿泊代・交通費・謝礼</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>20000</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>1</v>
@@ -816,140 +815,123 @@
         <f>B26*C26</f>
         <v/>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>謝礼1名分を計上。2人目は未払。宿泊代はホテル代に含む</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>コーチ宿泊代・交通費・謝礼</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>0</v>
+          <t>予備費未使用返金分※4</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>1000</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D27" s="7">
         <f>B27*C27</f>
         <v/>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>金額未確定（畠山先生に確認中）</t>
-        </is>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>予備費未使用返金分※4</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="D28" s="7">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>支出合計</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="11">
-        <f>SUM(D19:D28)</f>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="9">
+        <f>SUM(D18:D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>収支差額（収入－支出）</t>
+        </is>
+      </c>
+      <c r="D30" s="11">
+        <f>D14-D28</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>収支差額（収入－支出）</t>
-        </is>
-      </c>
-      <c r="D31" s="12">
-        <f>D15-D29</f>
-        <v/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>バス代差額（有料道路代・駐車場代など後日請求分）</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>未確定（実費請求が届き次第、マイナスとして入力）</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>バス代差額（有料道路代・駐車場代など後日請求分）</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>未確定（実費請求が届き次第、マイナスとして入力）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>合宿残金</t>
         </is>
       </c>
-      <c r="D33" s="14">
-        <f>D31-D32</f>
-        <v/>
+      <c r="D32" s="13">
+        <f>D30-D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>※1 ホテル請求書合計は菅平ホテル発行の請求書（支払済）の実額。上の内訳4行の合計との差額をこの行で吸収しています。</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>※1 ホテル請求書合計は菅平ホテル発行の請求書（支払済）の実額。上の内訳4行の合計との差額をこの行で吸収しています。</t>
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>※2 雑費は「合宿中使用経費」シートの領収書付き支出（会計分類C）の合計です。会計分類B（父母会予算で精算するもの）は含みません。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>※2 雑費は「合宿中使用経費」シートの領収書付き支出（会計分類C）の合計です。会計分類B（父母会予算で精算するもの）は含みません。</t>
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>※3 バス代は国際興業への見積額。有料道路代・駐車場代は合宿後に実費請求されるため、届き次第「バス代差額」に反映してください。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>※3 バス代は国際興業への見積額。有料道路代・駐車場代は合宿後に実費請求されるため、届き次第「バス代差額」に反映してください。</t>
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>※4 予備費は不参加者を除く全参加者から@1,000円徴収し、使用しなかったため全額返金します。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>※4 予備費は不参加者を除く全参加者から@1,000円徴収し、使用しなかったため全額返金します。</t>
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>※ コーチ宿泊代・交通費・謝礼（黄色セル）は金額未確定です。判明次第このセルに入力すれば、支出合計以下は自動で再計算されます。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>※ コーチ宿泊代・交通費・謝礼（黄色セル）は金額未確定です。判明次第このセルに入力すれば、支出合計以下は自動で再計算されます。</t>
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>※ 合宿残金は返金せず、合宿後のプロテイン代等、部の活動費に充当します。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>※ 合宿残金は返金せず、合宿後のプロテイン代等、部の活動費に充当します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>※ 対戦校への手土産・メディカル費等（会計分類B）は父母会予算から別途精算するため、上記の合宿費会計には含めていません。詳細は「父母会予算精算」シートを参照してください。</t>
         </is>
@@ -958,9 +940,9 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A6:E6"/>
@@ -976,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1039,7 +1021,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="15" t="n">
         <v>46236</v>
       </c>
       <c r="B4" s="6" t="n">
@@ -1075,7 +1057,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="15" t="n">
         <v>46236</v>
       </c>
       <c r="B5" s="6" t="n">
@@ -1111,7 +1093,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="15" t="n">
         <v>46236</v>
       </c>
       <c r="B6" s="6" t="n">
@@ -1143,7 +1125,7 @@
       <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="15" t="n">
         <v>46236</v>
       </c>
       <c r="B7" s="6" t="n">
@@ -1175,7 +1157,7 @@
       <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="15" t="n">
         <v>46240</v>
       </c>
       <c r="B8" s="6" t="n">
@@ -1211,7 +1193,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="15" t="n">
         <v>46240</v>
       </c>
       <c r="B9" s="6" t="n">
@@ -1243,7 +1225,7 @@
       <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="15" t="n">
         <v>46240</v>
       </c>
       <c r="B10" s="6" t="n">
@@ -1279,20 +1261,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="D11" s="1" t="inlineStr">
+      <c r="A11" s="15" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>星野コーチ</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>夏合宿 コーチ謝礼</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>占部</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>占部立替。日付は要確認。2人目のコーチ分は未計上</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>雑費 合計</t>
         </is>
       </c>
-      <c r="E11" s="12">
-        <f>SUM(E4:E10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>※ 今年度は7件。昨年度は雑費36件の記録があり、比較して記録漏れがないか確認してください。</t>
+      <c r="E12" s="11">
+        <f>SUM(E4:E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>※ 今年度は8件。昨年度は雑費36件の記録があり、比較して記録漏れがないか確認してください。</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1382,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="15" t="n">
         <v>46235</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1397,7 +1415,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -1435,7 +1453,7 @@
           <t>父母会予算 合計</t>
         </is>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>SUM(D4:D5)</f>
         <v/>
       </c>
